--- a/TOOLS/OMNIDIAG/EXPORTS/omnidiag_alarms_and_messages.xlsx
+++ b/TOOLS/OMNIDIAG/EXPORTS/omnidiag_alarms_and_messages.xlsx
@@ -571,12 +571,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NOT LocalIoValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication interne ou panne matérielle du module CPU Local_Digital_IO (Slot 1).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper la commande au pupitre. Noter le code ALM_001.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier voyant ERR/RUN sur la CPU VEICHI. Contrôler alimentation 24Vcc et connectique nappe de fond de panier.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 1 Local_Digital_IO ➔ Voyants CPU : RUN Vert fixe, ERR Éteint ➔ Mesure : 24Vcc entre bornes +24V et 0V</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -614,12 +626,24 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>NOT Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+          <t>🔌 Défaut de communication coupleur ou coupure 24V sur le module d'entrées VH_0800END (Slot 3).</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Couper les commandes au pupitre. Verrouiller le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier clip de verrouillage fond de panier Slot 3. Mesurer alimentation 24Vcc sur le bornier du module VH_0800END.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 3 VH_0800END ➔ Mesure : 24Vcc sur bornes d'alimentation module ➔ LED PWR allumée verte</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -657,12 +681,24 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NOT Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication ou panne d'alimentation du module mixte VH_0808ETP (Slot 2).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Interdiction translation et treuils au pupitre. Relever le code ALM_003.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler enfichage Slot 2 sur le rail DIN. Vérifier fusible protection 24Vcc de la carte VH_0808ETP.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 2 VH_0808ETP ➔ Mesure : 24Vcc sur bornes d'alimentation carte ➔ LED PWR allumée verte</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -700,12 +736,24 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>NOT Vh0008ErValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+          <t>🔌 Défaut d'alimentation ou défaillance du module 8 sorties relais VH_0008ER (Slot 4 - Freins).</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Interdiction des commandes treuils et translation au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier module Slot 4. Contrôler présence du 24Vcc sur les communs relais C0..C7 et la nappe interne.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 4 VH_0008ER ➔ Mesure : 24Vcc sur communs relais ➔ Vérifier étrier fond de panier bien enclenché</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -743,12 +791,24 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NOT Vh0008Er1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication ou d'alimentation du module sorties relais VH_0008ER_1 (Slot 5 - Sécurité).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Frapper l'arrêt d'urgence au pupitre. Condamner le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier Slot 5. Contrôler alimentation 24Vcc et boucle de maintien puissance PowerKeepAlive.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 5 VH_0008ER_1 ➔ Mesure : 24Vcc sur communs C6/C7 (%QX28.6/%QX28.7) ➔ Attendu : Relais fermés au réarmement puissance</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -786,12 +846,24 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NOT CanBusValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+          <t>📡 Défaillance générale du bus CANopen maître CPU (câble blindé coupé, parasite sévère, bus éteint).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes. Couper puis réenclencher l'alimentation générale du pupitre.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier résistance 120 Ω à chaque extrémité du bus CAN. Contrôler le blindage et la continuité des lignes CAN_H et CAN_L.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Port CANopen CPU VEICHI ➔ Mesure hors tension : 60 Ω entre CAN_H et CAN_L ➔ Sous tension : ~2.5Vcc sur CAN_H et CAN_L par rapport au 0V</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -829,12 +901,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CanBusValid AND NOT Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>📡 Joystick pupitre JOY1 non détecté sur le bus CANopen (Node ID 1 absent ou 24V pupitre coupé).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre le joystick physique au neutre mécanique. Couper et réarmer le commutateur pupitre.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler 24Vcc sur connecteur JOY1 sous pupitre. Vérifier l'état de la LED CANopen sous le manipulateur (Verte clignotante = Pre-Op).</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Connecteur JOY1 sous pupitre ➔ Mesure : 24Vcc entre broche 1 (+) et broche 2 (0V) ➔ Câble CAN blindé 2 paires</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -872,12 +956,24 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>NOT EcatBusValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>📡 Rupture de communication sur le maître EtherCAT automate (câble principal débranché ou perturbation CEM).</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes machine. Noter code ALM_008 au pupitre.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : inspecter câble Ethernet blindé RJ45 partant du port EtherCAT CPU vers le premier esclave (variateur AC600).</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Port EtherCAT CPU VEICHI ➔ LED Link/Act : Verte clignotante (trafic actif) ➔ Cordon Ethernet industriel blindé CAT5e/CAT6</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -915,12 +1011,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>📡 Codeur absolu COD1 treuil levage M1 non détecté sur le bus EtherCAT (câble touret M12 coupé ou 24V manquant).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer le treuil M1. Rester au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Treuil M1 : contrôler voyants LED (PWR, L/A) sur connecteur M12 du codeur COD1. Tester continuité des 4 paires du cordon en chaîne porte-câbles.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD1 (Treuil M1) ➔ Port M12 IN ➔ Attendu : 24Vcc broches 1-3, LED L/A Verte clignotante</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -958,12 +1066,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+          <t>📡 Codeur absolu COD2 treuil benne M2 non détecté sur le bus EtherCAT (câble touret M12 coupé ou 24V manquant).</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer le treuil M2. Rester au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Treuil M2 : contrôler voyants LED (PWR, L/A) sur connecteur M12 du codeur COD2. Tester cordon chaîne porte-câbles et disjoncteur 24V capteurs.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD2 (Treuil M2) ➔ Port M12 IN ➔ Attendu : 24Vcc broches 1-3, LED L/A Verte clignotante</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1001,12 +1121,24 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>📡 Variateur translation AC600 non détecté sur le bus EtherCAT (drive éteint ou câble RJ45 déconnecté).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Translation M3 immobilisée. Ne pas insister sur les commandes.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier disjoncteur alimentation Q_Drive variateur. Contrôler voyant LINK sur port RJ45 EtherCAT du drive AC600.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Variateur AC600 ➔ Port RJ45 EtherCAT IN ➔ Attendu : LED Link verte fixe/clignotante ➔ Disjoncteur drive enclenché</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1044,12 +1176,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication avec le pupitre ou heartbeat IHM interrompu pendant la commande de levage M1.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre les manipulateurs au neutre au pupitre. Vérifier l'écran IHM.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le réseau Ethernet IHM-PLC et l'alimentation 24V de la dalle tactile de supervision.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Port Ethernet IHM ➔ Ping IP automate VEICHI ➔ Diagnostic variable GVL_IHM.Commun.HeartbeatIhmOk</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1087,12 +1231,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorEncoder AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>📡 Perte de signal ou anomalie trame du codeur treuil M1 en mouvement (perte comptage position).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt du treuil M1. Ne pas passer en mode automatique. Mettre au neutre.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier fixation mécanique de l'axe codeur COD1 sur le tambour treuil M1. Contrôler connecteur M12 et blindage.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Variable PRG_02_Acquisition.Data.EncoderM1.Measurement.EncoderAvailable ➔ Attendu : TRUE</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1130,12 +1286,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+          <t>⚡ Détection d'une inversion de phase 400V ou coupure de phase pendant l'exploitation du treuil M1.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper les commandes au pupitre.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le relais de surveillance des phases en armoire tête. Mesurer tension 400Vac entre phases L1, L2, L3.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal ➔ 0V si défaut phase</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1173,12 +1341,24 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaA AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>🚨 Dérive non commandée M1 (Meca A) : rotation du tambour détectée &gt; 5.0m alors que les commandes et le frein sont coupés.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>🛑 NE TOUCHER À RIEN. Enclencher l'Arrêt d'Urgence coup de poing pupitre si le tambour continue de tourner sous la charge.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER GRAVITATIONNEL : Interdire l'accès sous la flèche. Armoire : mesurer 0V sur bobine frein M1. Remplacer les garnitures si patinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>VH_0008ER · %QX27.0 = 0 | VH_0800END · %IX225.0 = 0V ➔ Mesure bornier frein treuil M1 : 0V strict</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1216,12 +1396,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaB AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt M1 (Meca B) : contacteurs ou frein restés enclenchés &gt; 3s après retour au neutre du manipulateur.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur M1 au neutre. Contrôler visuellement l'arrêt complet du tambour treuil.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier si contacteur KM_M1 ou relais de défreinage reste mécaniquement coincé fermé. Contrôler varistance anti-arc.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · %IX0.0 (M1_ContactorsReleased_DI) ➔ Attendu repos : 24V | VH_0800END · %IX225.0 (BrakeOpen) ➔ Attendu repos : 0V</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1259,12 +1451,24 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaC AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>🚨 Glissement M1 pendant cycle benne (Meca C) : le treuil M1 a dérivé de plus de 2.0m alors qu'il devait maintenir la charge immobile.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de l'action benne. Mettre les manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le couple de serrage du frein treuil M1. Vérifier si la bobine de défreinage M1 n'a pas reçu d'alimentation parasite.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Mesure multimètre DC aux bornes bobine frein M1 pendant fermeture benne : 0V strict ➔ MecaCDriftM &gt; 2.0m</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1302,12 +1506,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaD AND LocalIoValid AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+          <t>🚨 Non-arrêt capteur haut M1 (Meca D) : le treuil a franchi le fin de course haut sans que l'arrêt ne soit confirmé sous 3s.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>🛑 ARRÊT IMMÉDIAT. Ne pas tenter de forcer la montée. Vérifier que la tête de flèche n'est pas en butée.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler détecteur inductif fin de course haut M1M2_TopPositionFree_DI (%IX0.7). Vérifier la chaîne de coupure contacteurs montée.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.7 (M1M2_TopPositionFree_DI) ➔ Attendu libre : 24V (Contact NC) | Ouvert en butée : 0V</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1345,12 +1561,24 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaE AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>🚨 Écart critique synchronisation M1/M2 (Meca E) : décalage entre câbles &gt; 7.0m en mouvement couplé solidaire.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre. Vérifier visuellement l'assiette et le comportement de la benne.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Relever positions codeurs M1 et M2 sur l'IHM. Vérifier si un tambour patine ou si un câble a sauté d'une gorge.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>IHM Synchro ➔ Écart brut ABS(CablePosM1 - CablePosM2 + ActiveOffsetM) &gt; 7.0m ➔ TonMecaE = 3s avant coupure puissance</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1388,12 +1616,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOppositeDir AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+          <t>🚨 Sens de rotation opposé M1 : le tambour tourne à l'envers de la commande demandée au manipulateur pendant plus de 1s.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener le manipulateur au neutre au pupitre. Ne pas forcer la commande.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'ordre des phases moteur sur contacteurs montée/descente KM1/KM2 en armoire. Vérifier polarité de comptage codeur COD1.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Mesure : Vitesse signée SignedSpeed_Mps ➔ Attendu : Même polarité que l'ordre RelayFwd/RelayRev</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1421,7 +1661,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>[M1] ErrorID:16 - absence mouvement</t>
+          <t>[M1] ErrorID:16 - discordance commande/retour/mouvement</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1431,12 +1671,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorNoMovement AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>⏱️ Absence de mouvement M1 : commande active et freins ouverts mais aucune progression de câble mesurée après 3s.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre. Vérifier visuellement si le câble ou le tambour est bloqué mécaniquement.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier disjoncteur moteur Q_M1 et présence tension 400Vac en sortie contacteurs de sens. Contrôler décollement mécanique frein.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.1 (M1_ThermalOk_DI) ➔ Mesure : 400Vac bornes moteur ➔ Attendu repos : 24Vcc sur %IX0.1 et 400Vac en commande</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1474,12 +1726,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOverspeed AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+          <t>⚠️ Survitesse treuil M1 détectée par le codeur COD1 au-delà de la bande maximale autorisée (SafeStop déclenché).</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur M1 au neutre. Laisser le treuil s'immobiliser sous rampe contrôlée.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'accouplement mécanique du codeur COD1. Vérifier si la charge n'entraîne pas le tambour au-delà de la vitesse nominale.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM ➔ Vitesse mesurée Speed_Mps &gt; SpeedBandMaxMps[5] ➔ SafeStop actif sans PowerCutOff</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1517,12 +1781,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>📡 Perte de communication opérateur ou coupure heartbeat IHM pendant la commande du treuil benne M2.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur benne au neutre au pupitre. Contrôler l'écran tactile.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le commutateur pupitre et la liaison Ethernet IHM-automate.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Port Ethernet IHM ➔ Ping IP automate VEICHI ➔ GVL_IHM.Commun.HeartbeatIhmOk</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1560,12 +1836,24 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorEncoder AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+          <t>📡 Perte de signal ou défaut de mesure du codeur absolu treuil M2 COD2.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des manœuvres benne. Manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le câble blindé M12 et la fixation de l'axe codeur COD2 sur le tambour M2.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD2 Treuil M2 ➔ Variable PRG_02_Acquisition.Data.EncoderM2.Measurement.EncoderAvailable ➔ Attendu : TRUE</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1603,12 +1891,24 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>⚡ Inversion ou coupure d'une phase réseau 400V pendant l'exploitation du treuil benne M2.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper les commandes au pupitre.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le relais de surveillance des phases en armoire tête. Mesurer tension triphasée 400Vac.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1646,12 +1946,24 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaA AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
+          <t>🚨 Dérive non commandée M2 (Meca A) : rotation du tambour treuil benne &gt; 5.0m sans commande active.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>🛑 NE TOUCHER À RIEN. Enclencher l'Arrêt d'Urgence pupitre si la benne descend toute seule.</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER : Condamner le pupitre. Armoire : mesurer 0V sur bobine frein M2. Remplacer les garnitures si patinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>VH_0008ER · %QX27.1 = 0 | VH_0800END · %IX225.1 = 0V ➔ Mesure bornier frein treuil M2 : 0V strict</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1689,12 +2001,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaB AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt M2 (Meca B) : contacteurs ou frein M2 restés enclenchés &gt; 3s après retour au neutre.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur benne au neutre. Contrôler l'arrêt complet du tambour treuil M2.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler retombée mécanique du contacteur KM_M2 et relais frein. Remplacer si contacts collés.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · %IX0.2 (M2_ContactorsReleased_DI) ➔ Attendu repos : 24V | VH_0800END · %IX225.1 (BrakeOpen) ➔ Attendu : 0V</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1732,12 +2056,24 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaC AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
+          <t>🚨 Glissement M2 pendant benne figée (Meca C) : dérive anormale du tambour benne M2.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la manœuvre. Mettre les manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier étanchéité et réglage entrefer frein M2. Mesurer absence de tension sur bobine frein M2.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Bornier frein treuil M2 ➔ Mesure : Tension bobine frein ➔ Attendu : 0Vcc et dérive MecaCDriftM &lt; 2.0m</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1775,12 +2111,24 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaD AND LocalIoValid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>🚨 Non-arrêt capteur haut M2 (Meca D) : treuil benne ayant dépassé le fin de course haut sans s'arrêter sous 3s.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>🛑 ARRÊT IMMÉDIAT. Ne pas forcer la montée. Vérifier que le câble n'est pas en butée contre le tambour.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler détecteur inductif fin de course haut M1M2_TopPositionFree_DI (%IX0.7) et contacteurs montée M2.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.7 (M1M2_TopPositionFree_DI) ➔ Attendu libre : 24V | Ouvert : 0V</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1818,12 +2166,24 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaE AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
+          <t>🚨 Écart critique synchronisation M2/M1 (Meca E) : dérive différentielle des treuils &gt; 7.0m en marche couplée.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre. Vérifier l'état visuel des câbles sur le ponton.</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler valeurs de position COD1 et COD2 sur IHM. Vérifier absence de glissement câble dans les tambours.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM Synchro ➔ Écart absolu &gt; 7.0m ➔ TonMecaE = 3s avant coupure puissance</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1861,12 +2221,24 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOppositeDir AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>🚨 Sens de rotation opposé M2 : rotation du tambour à l'envers de la commande demandée pendant plus de 1s.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler câblage phases puissance moteur M2 sur contacteurs KM_M2. Vérifier sens comptage codeur COD2.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD2 Treuil M2 ➔ Mesure : Vitesse signée SignedSpeed_Mps ➔ Attendu : Même polarité que l'ordre RelayFwd/RelayRev</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1894,7 +2266,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>[M2] ErrorID:16 - absence mouvement</t>
+          <t>[M2] ErrorID:16 - discordance commande/retour/mouvement</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1904,12 +2276,24 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorNoMovement AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr"/>
+          <t>⏱️ Absence de mouvement M2 : commande active et frein ouvert mais aucune rotation mesurée après 3s.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur au neutre. Contrôler visuellement si la benne ou le tambour est coincé.</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler disjoncteur moteur Q_M2 et présence 400Vac aux bornes moteur. Contrôler défreinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.3 (M2_ThermalOk_DI) ➔ Mesure : 400Vac bornes moteur ➔ Attendu repos : 24Vcc sur %IX0.3 et 400Vac en commande</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1947,12 +2331,24 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOverspeed AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>⚠️ Survitesse treuil M2 détectée par codeur COD2 au-delà du palier 5 (SafeStop activé).</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur benne au neutre. Attendre l'arrêt complet sous rampe.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'accouplement du codeur COD2. Vérifier absence d'emballement sous le poids de la benne.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM ➔ Vitesse mesurée Speed_Mps &gt; SpeedBandMaxMps[5] ➔ SafeStop actif</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -1990,12 +2386,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication opérateur pupitre pendant la commande de translation portique M3.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre le manipulateur translation au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler bus CANopen JOY1 et heartbeat supervision IHM.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Bus CANopen Pupitre ➔ Diagnostic trames CAN ➔ Attendu : NMT Operational et HeartbeatIhmOk = TRUE</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2033,12 +2441,24 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorDriveComm AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>📡 Perte de communication bus EtherCAT avec le variateur translation VEICHI AC600.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Translation bloquée. Mettre les commandes au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler cordon RJ45 EtherCAT reliant l'automate au variateur AC600. Vérifier alimentation commande drive.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Variateur AC600 ➔ Port EtherCAT IN ➔ Attendu : Câble RJ45 connecté, LED Link/Act verte clignotante</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2076,12 +2496,24 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
+          <t>⚡ Rotation de phase 400V incorrecte ou perte de phase sur l'alimentation de la translation.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine au pupitre.</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier relais de phases et tension 400Vac en amont du variateur AC600.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal</t>
+        </is>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2119,12 +2551,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorMecaB AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt translation (Meca B) : variateur ou frein M3 toujours actifs &gt; 3s après stop.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre. Vérifier visuellement l'immobilisation du portique.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier contacteur frein translation KM_Frein_M3 et sortie fréquence variateur AC600.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.2 (M3_BrakeIsOpen_DI) ➔ Attendu arrêt : 0V | Variateur AC600 : Fréquence &lt; 0.5 Hz</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2162,12 +2606,24 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorMecaA AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
+          <t>🚨 Mouvement non commandé translation (Meca A) : déplacement portique détecté sans consigne active après 1s.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Frapper l'Arrêt d'Urgence pupitre si le portique dérive le long des rails sous l'effet du vent.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER : Condamner le portique avec cales rail. Armoire : mesurer 0V sur bobine frein translation. Remplacer patins de frein si usés.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Bornier armoire frein M3 ➔ Mesure : 0V strict ➔ Variateur AC600 : Fréquence mesurée &gt; 0.5 Hz sans commande</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2205,12 +2661,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorLimitSwitch AND Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>🚨 Fin de course extrême translation actionné (dépassement zone Trémie ou Maintenance).</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne plus avancer vers la butée. Passer en dérogation au pupitre pour reculer hors de la zone.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier palpeur inductif came extrême sur voie de roulement. Contrôler boîte de raccordement chariot.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Borne %IX224.0 (Trémie) ou %IX224.4 (Maintenance) ➔ Mesure : 24Vcc sur la came concernée</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2248,12 +2716,24 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorSensorIncoherent AND Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+          <t>📐 Combinaison de cames translation physiquement impossible (ex: Trémie et Maintenance actives en même temps).</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes translation au pupitre. Relever la position visuelle approximative du portique.</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Inspecter les 5 capteurs inductifs de cames translation le long des rails (boue, graviers, câbles blessés).</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Bornes %IX224.0 à %IX224.4 ➔ Mesure 24Vcc : Une seule came active autorisée à la fois</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2291,12 +2771,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>⚡ Défaut séquence / retour frein translation M3 (discordance entre ordre défreinage et recopie armoire).</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : tester contacteur relais frein KM_Frein_M3. Mesurer tension bobine défreinage en manœuvre.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>VH_0008ER · Relais %QX27.2 (Cmd) vs VH_0800END · Borne %IX225.2 (Retour %IX225.2) ➔ Concordance exigée sous 500 ms</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2334,12 +2826,24 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0008) &lt;&gt; 16#0000) AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+          <t>⚡ Défaut variateur translation AC600 (surcharge, surintensité, sous-tension bus continu ou défaut thermique).</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre au pupitre. Patienter 5 min pour refroidissement.</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : relever le code affiché sur le bandeau digital du variateur AC600 (ex: E.OC, E.OL, E.LU). Contrôler résistance de freinage.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Afficheur variateur AC600 ➔ Code défaut | Mesure bus DC : ~560Vcc entre bornes (+) et (-)</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2377,12 +2881,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>🛑 Butée mécanique finale de translation atteinte (arrêt immédiat sur bordure de voie).</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser le manipulateur pour dégager le portique en sens inverse.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler amortisseurs de fin de course rail et état mécanique du linguet de déclenchement.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Bornes %IX224.0 ou %IX224.4 ➔ Mesure : 24Vcc entre borne et 0V ➔ Attendu hors butée : 0V (Détecteur inductif NO libre)</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2420,12 +2936,24 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>(TranslationFinalInterlockErrorId &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
+          <t>🔒 Barrière finale translation active : interlock frein ou redémarrage engagé nécessitant un acquittement explicite.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener le manipulateur au neutre. Appuyer sur le bouton Acquittement / Reset au pupitre.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier mot d'état TranslationFinalInterlockErrorId sur l'écran de diagnostic IHM.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Pupitre / IHM ➔ Diagnostic variable TranslationFinalInterlockErrorId ➔ Attendu : Valeur 0 après front montant bouton Reset</t>
+        </is>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2463,12 +2991,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>⚙️ Configuration géométrie benne invalide (offset fermé inférieur ou égal à l'offset ouvert en mémoire).</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer la benne au pupitre.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>💻 IHM Réglages : vérifier paramètres géométrie benne. L'offset fermé doit être supérieur à l'offset ouvert (nominal 15.0m &gt; 0.0m).</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>IHM Réglages Benne ➔ Variables OffsetCloseM vs OffsetOpenM ➔ Attendu : OffsetCloseM (nom. 15.0m) strictement supérieur à OffsetOpenM (0.0m)</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2506,12 +3046,24 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
+          <t>🪣 Dépassement écart maximum autorisé benne : décalage M2 - M1 hors plage physique plausible (&gt; 17m ou &lt; -1m).</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Passer en mode Manuel Dérogation : ramener visuellement la benne dans une position intermédiaire normale.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier position codeurs M1 et M2. Vérifier absence de glissement de câble ou de mou exagéré.</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>IHM Benne ➔ Écart mesuré CablePosM2 - CablePosM1 ➔ Attendu : Compris dans l'intervalle [-1.0m .. 17.0m]</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2549,12 +3101,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0004) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout déplacement benne : la benne n'a pas atteint sa position ouverte ou fermée sous 60 secondes.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre. Vérifier visuellement si la benne est coincée dans le matériau.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler vitesse treuil M2 et état mécanique des poulies de fermeture benne.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Bloc FB_Bucket ➔ Temporisateur interne TonTimeout ➔ Attendu : Temps écoulé ET &lt; CfgTimeoutDuration (T#60s)</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2592,12 +3156,24 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
+          <t>🚨 Glissement treuil M1 détecté pendant manœuvre benne (&gt; 1.0m de mouvement flèche non autorisé).</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt de la commande benne. Ramener au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler frein treuil M1 et absence de rotation parasite pendant l'actionnement du treuil M2.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Treuil M1 ➔ Écart position ABS(CablePosM1 - M1RefPosM) ➔ Attendu : Dérive &lt; 1.0m pendant manœuvre benne</t>
+        </is>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2635,12 +3211,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0010) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>📍 Codeurs treuils non référencés pour la séquence benne (homing machine non validé après mise sous tension).</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Effectuer la procédure de référencement machine (Homing) au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>💻 Vérifier drapeaux HomedM1 et HomedM2 sur la page diagnostic superviseur.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Supervision IHM / PLC ➔ Variables HomedAndReliableM1 et HomedAndReliableM2 ➔ Attendu : État TRUE sur les deux axes</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2678,12 +3266,24 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>((SyncErrorId AND 16#0001) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
+          <t>⚠️ Écart de synchronisation M1/M2 supérieur à 6.0m en marche couplée (SafeStop activé).</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre. Vérifier visuellement la planéité des câbles.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler vitesse respective des tambours M1 et M2. Recaler l'assiette en pilotage unitaire si nécessaire.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>FB_SyncDeviation ➔ Écart calculé DeltaPosM ➔ Attendu : DeltaPosM &lt; 6.0m (seuil d'arrêt)</t>
+        </is>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2721,12 +3321,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>((SyncErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>🔀 Discordance contacteurs M1/M2 en marche synchronisée (un treuil commandé et pas l'autre ou paliers différents).</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier la chaîne de commande des contacteurs de sens et paliers M1 et M2. Contrôler relais de sortie.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>FB_SyncContactor ➔ Variable ContactorMismatch ➔ Attendu repos / marche couplée : FALSE (Vecteurs identiques)</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2764,12 +3376,24 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr"/>
+          <t>⏱️ Timeout immersion cycle automatique : temps d'atteinte de la surface d'eau dépassé.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en mode Manuel au pupitre. Remonter la benne en surface.</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier réglage altimétrique du plan d'eau (ImmersionUpper_M) sur l'IHM cycle.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Bloc FB_CycleSemiAuto ➔ Temporisateur phase plongée ➔ Attendu : Atteinte plan d'eau avant expiration T#Timeout</t>
+        </is>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2807,12 +3431,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout détection fond : la benne descend sous l'eau sans toucher le fond dans le temps alloué.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Stopper la descente automatique. Repasser en manuel au pupitre.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler fonctionnement palpeur Kobold ou seuil altimétrique de profondeur fond.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Bloc FB_CycleSemiAuto ➔ Temporisateur descente fond ➔ Attendu : Contact fond avant seuil temps alloué</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2850,12 +3486,24 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0004) &lt;&gt; 16#0000) AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
+          <t>🛑 Limite basse de plongée atteinte : la benne a atteint la profondeur maximale autorisée.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser la commande pour remonter la benne au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier seuil de profondeur légale CfgCableLimitDescentM sur la page configuration IHM.</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Variable CablePosM1 ➔ Attendu : Position supérieure à CfgCableLimitDescentM (-50.0m)</t>
+        </is>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2893,12 +3541,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>🌊 Contact fond perdu pendant l'extraction (glissement de la benne dans la boue ou perte signal Kobold).</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Arrêter la montée rapide. Passer en manuel lent pour assurer la fermeture.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler capteur palpeur Kobold (%IX0.5) et liaison électrique touret.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.5 (KoboldBottomTouch_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu : 24V reposée au fond (0V en suspension)</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2936,12 +3596,24 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0010) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
+          <t>🪢 Perte tension câble benne M2 sous l'eau (mou de câble détecté par la roulette palpeuse).</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Passer en manuel dérogation au pupitre : retendre doucement le câble M2.</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier mécanique bras palpeur anti-mou sur tambour M2 et propreté de l'interrupteur.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.4 (M2_TensionedCable_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu câble tendu : 24V (Contact NC fermé)</t>
+        </is>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -2979,12 +3651,24 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0020) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>⚠️ Anomalie de vitesse treuils pendant la phase de plongée (dérive d'accélération sous l'eau).</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener commandes au neutre au pupitre. Laisser la charge se stabiliser.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler régularité vitesse codeurs M1 et M2 en plongée.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Codeurs COD1/COD2 ➔ Dérivée d(Speed_Mps)/dt en plongée ➔ Attendu : Accélération stable dans le gabarit défini</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3022,12 +3706,24 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
+          <t>⚙️ Configuration de plongée invalide (paramètres altimétriques immersion / fond incohérents).</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Cycle semi-auto refusé. Relever paramètres IHM au pupitre.</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier cohérence paramètres cycle plongée sur le superviseur.</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>IHM Recettes Dragage ➔ Variables GVL_IHM.CycleSemiAuto.Cfg ➔ Attendu : Cohérence altimétrique Fond &lt; Immersion &lt; Crête</t>
+        </is>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3065,12 +3761,24 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0001) &lt;&gt; 16#0000) AND LocalIoValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>🌊 Défaut contact fond pendant la phase d'extraction des matériaux.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en manuel au pupitre. Vérifier tension des câbles.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler capteur de fond et seuil d'effort sur treuils.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.5 (KoboldBottomTouch_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu : 24V au fond</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3108,12 +3816,24 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
+          <t>🪣 Défaut fermeture benne pendant l'extraction (benne n'atteignant pas l'état fermé sous l'eau).</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en commande manuelle benne M2 pour forcer la fermeture au pupitre.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler absence d'enrochement coincé dans les mâchoires de la benne.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Supervision IHM ➔ Variable _BucketState.IsClosed ➔ Attendu : Confirmation TRUE sous 60s max</t>
+        </is>
+      </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3151,12 +3871,24 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0004) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>⏱️ Défaut contrôle vitesse montée lors de l'extraction initiale (distance de contrôle non franchie).</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier passage au palier 1 pendant la traversée de la zone ExtractionControlDistance_M.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Contacteurs Paliers Vitesse ➔ Relais palier 1 KM_P1 (%QX27.4) ➔ Attendu : Enclenchement exclusif du Palier 1 dans zone décollement</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3194,12 +3926,24 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr"/>
+          <t>⚙️ Configuration extraction cycle automatique invalide.</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Bloquer cycle auto au pupitre.</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>💻 Revoir paramètres de la phase extraction sur l'écran IHM.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>IHM Recettes Dragage ➔ Variables GVL_IHM.CycleSemiAuto.Cfg ➔ Attendu : Cohérence paramètres d'extraction</t>
+        </is>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3237,12 +3981,24 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>🚨 Discordance redondance contacteurs de puissance ligne ou relais de sécurité AU (contact miroir non retombé).</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>🛑 COUPURE GÉNÉRALE. Frapper coup de poing Arrêt d'Urgence pupitre. Condamner le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER DE MORT 400V : Consigner la source quai/groupe + VAT. Contrôler les contacts miroirs NC du contacteur de ligne KM_Power et blocs auxiliaires de sécurité.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Bornes %IX225.6 et %IX225.7 ➔ Mesure : 24Vcc / 0V entre bornes et 0V carte ➔ Attendu réarmé : 24Vcc sur les deux voies</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3280,12 +4036,24 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
+          <t>🚨 Échec confirmation armement puissance (le contacteur de ligne ne s'enclenche pas sous 2s après commande).</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Relâcher le bouton Réarmement. Vérifier que tous les AU sont déverrouillés au pupitre.</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier bobine contacteur ligne KM_Power, fusible commande 24V et module sécurité AU.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>VH_0008ER_1 · Relais %QX28.6/%QX28.7 (PowerKeepAlive) ➔ Mesure : 24Vcc sur bobine KM_Power ➔ Attendu : 24Vcc après appui réarmement</t>
+        </is>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3323,12 +4091,24 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>🚨 Échec autotest démarrage chaîne d'urgence (défaut de retombée d'un canal lors du test d'initialisation).</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Redémarrage puissance refusé. Condamner le pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler les contacts de recopie de tous les relais de sécurité en armoire électrique.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Bloc Sécurité FB_Safety_EmergencyManagement ➔ Contrôle retombée des canaux d'urgence ➔ Attendu : 0V strict sur toutes les lignes avant réarmement</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3366,12 +4146,24 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0001) &lt;&gt; 16#0000) AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>🛑 Profondeur limite légale atteinte en cycle automatique (arrêt fond de fouille autorisé).</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser les commandes au pupitre pour remonter la benne. Ne pas descendre plus bas.</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier valeur de la limite légale autorisée sur l'écran réglages IHM.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>IHM Configuration Cycle ➔ Variable CablePosM1 vs LimitLegalDepthMinAllowed_M ➔ Attendu : CablePosM1 supérieur à la limite légale</t>
+        </is>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3409,12 +4201,24 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0002) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>⚠️ Défaut de synchronisation des treuils en cours de cycle automatique.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Stopper le cycle semi-auto au pupitre. Repasser en manuel.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler équilibrage de charge et vitesses relatives M1/M2.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Supervision Cycle ➔ Mot CycleErrorId bit 1 ➔ Attendu : Écart M1/M2 dans le gabarit cycle semi-auto</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3452,12 +4256,24 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0008) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
+          <t>⚠️ Écart codeurs excessif constaté pendant la phase de remontée de charge.</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener commandes au neutre au pupitre. Vérifier assiette benne.</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler absence de glissement mécanique sur l'un des deux tambours de treuil.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Codeurs COD1/COD2 ➔ Mot CycleErrorId bit 3 ➔ Attendu : Écart codeurs en montée inférieur au seuil critique</t>
+        </is>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3495,12 +4311,24 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0010) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>⚠️ Écart de vitesse confirmé entre treuils M1 et M2 en déplacement couplé.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre les manipulateurs au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler contacteurs de paliers de vitesse en armoire (KM_P1 à KM_P5).</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Supervision Moteurs ➔ Mot CycleErrorId bit 4 ➔ Attendu : Concordance des vitesses treuils en marche couplée</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3538,12 +4366,24 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0020) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication avec le pupitre IHM pendant le déroulement d'un cycle automatique.</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Le cycle s'interrompt en sécurité. Vérifier l'écran IHM au poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler câble réseau Ethernet blindé et switch réseau armoire.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Liaison Ethernet IHM ➔ Mot CycleErrorId bit 5 ➔ Attendu : HeartbeatIhmOk maintenu actif en continu</t>
+        </is>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -3581,12 +4421,24 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout d'étape cycle automatique : l'étape active du cycle a dépassé sa durée maximale allouée.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en mode Manuel au pupitre de commande. Dégager la machine si nécessaire.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>💻 Contrôler le numéro d'étape bloquée E_AutoCycleStep sur la page de supervision.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>FB_CycleSemiAuto ➔ Temporisateur d'étape active ➔ Attendu : Transition d'étape accomplie avant expiration timeout</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -10466,17 +11318,17 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Mettre les manipulateurs treuils au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre les manipulateurs au neutre sur le pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>🧰 Tester le contacteur frein M1 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts collés.</t>
+          <t>🧰 Tester le contacteur frein KM_Frein_M1 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Cmd: M1_BrakeRelease_RQ (VH_0008ER · %QX27.0) | Retour: M1_BrakeIsOpen_DI (VH_0800END · %IX225.0)</t>
+          <t>VH_0008ER · Relais %QX27.0 (M1_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C0/NO0 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.0 (M1_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -10521,17 +11373,17 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Mettre le manipulateur benne au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre le manipulateur benne au neutre au pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>🧰 Tester le contacteur frein M2 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
+          <t>🧰 Tester le contacteur frein KM_Frein_M2 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>Cmd: M2_BrakeRelease_RQ (VH_0008ER · %QX27.1) | Retour: M2_BrakeIsOpen_DI (VH_0800END · %IX225.1)</t>
+          <t>VH_0008ER · Relais %QX27.1 (M2_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C1/NO1 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.1 (M2_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
@@ -10576,17 +11428,17 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Mettre le manipulateur translation au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre le manipulateur translation au neutre au pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le relais/contacteur frein M3 en armoire. Mesurer 0V sur la bobine à l'arrêt.</t>
+          <t>🧰 Contrôler le relais frein KM_Frein_M3 en armoire. Mesurer 0V sur la bobine à l'arrêt.</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Cmd: M3_BrakeRelease_RQ (VH_0008ER · %QX27.2) | Retour: M3_BrakeIsOpen_DI (VH_0800END · %IX225.2)</t>
+          <t>VH_0008ER · Relais %QX27.2 (M3_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C2/NO2 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.2 (M3_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -10626,22 +11478,22 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>🚨 Contacteur de puissance sens/vitesse M1 resté collé fermé ou contact auxiliaire NC coupé.</t>
+          <t>🚨 Contacteur de puissance sens/vitesse M1 resté collé fermé ou boucle de surveillance EDM ouverte.</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas enclencher la puissance. Couper les commandes en cabine.</t>
+          <t>🛑 Ne pas enclencher la puissance. Condamner le pupitre de commande.</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>🧰 Consigner armoire. Contrôler les pôles de puissance du contacteur KM_M1 et les auxiliaires NO. Remplacer si soudé.</t>
+          <t>⚠️ DANGER 400V : Consigner l'armoire + VAT. Contrôler les pôles de puissance KM_M1 et la chaîne des contacts miroirs NC en série. Remplacer le contacteur si soudé.</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_ContactorsReleased_DI (Local_Digital_IO · %IX0.0) | Cmd: M1_RelayAscent/Descent_DQ (%QX0.0, %QX0.1)</t>
+          <t>Local_Digital_IO · Borne %IX0.0 (M1_ContactorsReleased_DI) ➔ Mesure : 24Vcc / 0V entre borne et 0V carte ➔ Attendu repos : 24V (Contacts miroirs NC fermés en série)</t>
         </is>
       </c>
       <c r="J235" s="3" t="inlineStr">
@@ -10681,22 +11533,22 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>🚨 Contacteur de puissance sens/vitesse M2 resté collé fermé ou contact auxiliaire NC coupé.</t>
+          <t>🚨 Contacteur de puissance sens/vitesse M2 resté collé fermé ou boucle de surveillance EDM ouverte.</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>🛑 Ne pas enclencher la puissance. Couper les commandes en cabine.</t>
+          <t>🛑 Ne pas enclencher la puissance. Condamner le pupitre de commande.</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>🧰 Consigner armoire. Contrôler les pôles de puissance du contacteur KM_M2 et les auxiliaires NO. Remplacer si soudé.</t>
+          <t>⚠️ DANGER 400V : Consigner l'armoire + VAT. Contrôler les pôles de puissance KM_M2 et la chaîne des contacts miroirs NC en série. Remplacer le contacteur si soudé.</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Retour: M2_ContactorsReleased_DI (Local_Digital_IO · %IX0.2) | Cmd: M2_RelayAscent/Descent_DQ (%QX0.2, %QX0.3)</t>
+          <t>Local_Digital_IO · Borne %IX0.2 (M2_ContactorsReleased_DI) ➔ Mesure : 24Vcc / 0V entre borne et 0V carte ➔ Attendu repos : 24V (Contacts miroirs NC fermés en série)</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -10741,7 +11593,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>⏳ Laisser refroidir 15 min. Vérifier absence de blocage mécanique visuel sur le treuil.</t>
+          <t>⏳ Laisser refroidir 15 min. Vérifier visuellement l'absence d'obstacle mécanique sur le treuil M1.</t>
         </is>
       </c>
       <c r="H237" s="3" t="inlineStr">
@@ -10751,7 +11603,7 @@
       </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_ThermalOk_DI (Local_Digital_IO · %IX0.1 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.1 (M1_ThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC disjoncteur fermé)</t>
         </is>
       </c>
       <c r="J237" s="3" t="inlineStr">
@@ -10791,12 +11643,12 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>🔥 Disjoncteur moteur M2 déclenché ou défaut de la moto-ventilation forcée.</t>
+          <t>🔥 Disjoncteur moteur M2 déclenché ou défaut moto-ventilation forcée.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>⏳ Laisser refroidir 15 min. Vérifier que la benne n'est pas coincée.</t>
+          <t>⏳ Laisser refroidir 15 min. Vérifier visuellement que la benne n'est pas bloquée.</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -10806,7 +11658,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Retour: M2_ThermalOk_DI (Local_Digital_IO · %IX0.3 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.3 (M2_ThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC disjoncteur fermé)</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -10851,17 +11703,17 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas lancer de mouvement treuils ou translation.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuils ou translation au pupitre.</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>🧰 Armoire : mesurer résistance ohmique des bobines freins M1/M2/M3 et ponts redresseurs. Réarmer disjoncteur freins.</t>
+          <t>🧰 Armoire : mesurer résistance ohmique des bobines freins M1/M2/M3 et ponts redresseurs. Réarmer disjoncteur freins Q_Freins.</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_M2_M3_BrakeThermalOk_DI (VH_0800END · %IX225.3 · contact NC)</t>
+          <t>VH_0800END · Borne %IX225.3 (M1_M2_M3_BrakeThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC fermé)</t>
         </is>
       </c>
       <c r="J239" s="3" t="inlineStr">
@@ -10906,17 +11758,17 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>👀 Vérifier le voltmètre général en cabine et la source d'alimentation (groupe ou réseau quai).</t>
+          <t>👀 Vérifier le voltmètre réseau au poste de conduite et la source d'alimentation (groupe ou réseau quai).</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>🧰 Armoire tête : vérifier LEDs relais phases. Mesurer 400V entre phases. Permuter 2 phases amont si inversion.</t>
+          <t>🧰 Armoire tête : vérifier LEDs relais de surveillance phases. Mesurer 400Vac équilibré entre phases. Permuter 2 phases amont si inversion.</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Retour: PhaseRotationOk_DI (VH_0800END · %IX225.4 · contact NC)</t>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Relais phases actif)</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -10956,12 +11808,12 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>🪢 Câble benne mou (benne posée au sol ou au fond de l'eau) ou roulette palpeuse anti-mou bloquée.</t>
+          <t>🪢 Câble benne détendu (benne posée au sol ou au fond de l'eau) ou roulette palpeuse anti-mou bloquée.</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Passer en manuel lent / dérogation : retendre doucement le câble M2 jusqu'à extinction du voyant mou.</t>
+          <t>🕹️ Passer en manuel lent / dérogation au pupitre : retendre doucement le câble M2 jusqu'à extinction du voyant mou.</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -10971,7 +11823,7 @@
       </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
-          <t>Retour: M2_TensionedCable_DI (Local_Digital_IO · %IX0.4 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.4 (M2_TensionedCable_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu câble tendu : 24V (Contact NC fermé)</t>
         </is>
       </c>
       <c r="J241" s="3" t="inlineStr">
@@ -11011,22 +11863,22 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>📐 Combinaison capteurs translation M3 impossible (ex: Trémie et Maintenance actives en même temps).</t>
+          <t>🪣 Benne détectée non fermée à la mise sous tension (état ouvert ou indéterminé).</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>👀 Vérifier visuellement la position du portique sur les rails de roulement.</t>
+          <t>🕹️ Mettre sélecteur treuil sur Benne (M2). Actionner la commande de fermeture benne jusqu'au voyant benne fermée.</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>🧰 Voie de roulement : tester les détecteurs inductifs de cames translation M3. Nettoyer les capteurs et vérifier la boîte chariot.</t>
+          <t>💻 Vérifier cohérence valeur codeur M2 vs M1 (OffsetCloseM ~ 15 m) sur l'écran diagnostic IHM.</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Entrées cames: M3_PosTremie..M3_PosMaintenance (VH_0808ETP · %IX224.0 à %IX224.4)</t>
+          <t>Diagnostic IHM · Variable _BucketState.IsClosed ➔ Attendu : TRUE après fermeture complète (Delta M2-M1 conforme)</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -11066,22 +11918,22 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>🚨 DANGER CRITIQUE : contacteur général puissance fermé alors que la boucle arrêt d'urgence est ouverte (pôles soudés).</t>
+          <t>🚨 Arrêt d'urgence percuté sur le pupitre de commande ou chaîne de sécurité ouverte.</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>🛑 COUPURE GÉNÉRALE IMMÉDIATE. Frapper coup de poing AU cabine ou couper disjoncteur général. Évacuer la machine.</t>
+          <t>👀 Vérifier et déverrouiller tous les coups de poing AU (pupitre, passerelle, armoire). Appuyer sur Réarmement AU.</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DANGER DE MORT. Consigner l'alimentation à la source. Remplacer contacteur ligne puissance KM_Power et contrôler le bloc sécurité AU.</t>
+          <t>🧰 Contrôler tension 24V sur boucle de sécurité AU et retombée des canaux du bloc de sécurité.</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr">
         <is>
-          <t>Retours: PowerContactorEngaged_DI (%IX225.6) et EmergencyChainClosed_DI (%IX225.7) sur VH_0800END</t>
+          <t>VH_0800END · Borne %IX225.7 (EmergencyChainClosed_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu réarmé : 24V</t>
         </is>
       </c>
       <c r="J243" s="3" t="inlineStr">
@@ -11121,22 +11973,22 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>📡 Perte communication bus codeur M1 ou coupure de l'alimentation 24V capteur.</t>
+          <t>📡 Joystick non détecté sur le bus CANopen (coupure alimentation 24V pupitre ou câble CAN coupé).</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>🛑 Ne pas passer en mode Semi-Auto ou Automatique.</t>
+          <t>🛑 Couper et réenclencher l'interrupteur d'alimentation du pupitre de commande. Relever le code d'erreur affiché.</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>🧰 Treuil M1 : contrôler voyants LED sur codeur absolu (Node 1). Vérifier connecteur M12, blindage câble et alim 24V.</t>
+          <t>🧰 Contrôler 24Vcc sur connecteur manipulateur sous pupitre. Vérifier continuité CAN_H / CAN_L et résistance de terminaison 120 Ω.</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Bus codeur: COD1_CODEUR (Node 1) | Alim 24V codeur M1</t>
+          <t>Bus CANopen Pupitre ➔ Mesure : 24Vcc alim broches 1-2 | 60 Ω entre CAN_H et CAN_L ligne éteinte</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -11176,22 +12028,22 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>📡 Perte communication bus codeur M2 ou connecteur M12 desserré sur touret.</t>
+          <t>📡 Codeur absolu EtherCAT treuil M1 non opérationnel (câble M12 Ethernet débranché ou perte alimentation 24V).</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas passer en mode Semi-Auto ou Automatique.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuil M1. Vérifier voyant bus sur l'écran IHM.</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>🧰 Treuil M2 : contrôler voyants LED sur codeur absolu (Node 2). Inspecter le câble souple de touret et la connectique M12.</t>
+          <t>🧰 Treuil M1 : contrôler LED d'état sur le codeur COD1 (L/A clignotante = trafic actif). Tester cordon M12 et présence 24Vcc.</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>Bus codeur: COD2_CODEUR (Node 2) | Alim 24V codeur M2</t>
+          <t>Codeur COD1 Treuil M1 ➔ Port M12 IN (EtherCAT) ➔ Attendu : LED L/A Verte clignotante, 24Vcc présent sur broches d'alimentation</t>
         </is>
       </c>
       <c r="J245" s="3" t="inlineStr">
@@ -11231,22 +12083,22 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>🎯 Treuil M1 non référencé depuis mise sous tension ou position mesurée en dehors de l'épure autorisée.</t>
+          <t>📡 Codeur absolu EtherCAT treuil M2 non opérationnel (câble M12 Ethernet débranché ou perte alimentation 24V).</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Sélectionner l'écran Homing en cabine et lancer la procédure de référencement guidée M1.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuil M2. Vérifier voyant bus sur l'écran IHM.</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le capteur came zéro de homing M1. Vérifier l'offset de référence et les seuils de butées logicielles dans CODESYS.</t>
+          <t>🧰 Treuil M2 : contrôler LED d'état sur le codeur COD2 (L/A clignotante = trafic actif). Tester cordon M12 et présence 24Vcc.</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Détecteur zéro homing: M1M2_TopPositionFree_DI (Local_Digital_IO · %IX0.7) | Config: GVL_Config</t>
+          <t>Codeur COD2 Treuil M2 ➔ Port M12 IN (EtherCAT) ➔ Attendu : LED L/A Verte clignotante, 24Vcc présent sur broches d'alimentation</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -11286,22 +12138,22 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>🎯 Treuil M2 non calibré (homing requis) ou position de benne hors plage admissible.</t>
+          <t>⚡ Variateur translation AC600 hors ligne ou en défaut (coupure réseau EtherCAT, disjoncteur variateur déclenché).</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Sélectionner l'écran Homing en cabine et lancer la procédure de référencement guidée M2.</t>
+          <t>🛑 Ne pas tenter de déplacer le chariot au pupitre. Relever le code variateur sur l'IHM.</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le capteur de référence zéro benne M2. Vérifier les limites de course logicielles haute et basse dans CODESYS.</t>
+          <t>🧰 Armoire : vérifier affichage LED sur le variateur AC600. Contrôler disjoncteur drive Q_Drive et câble RJ45 EtherCAT.</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
         <is>
-          <t>Détecteur zéro homing: M1M2_TopPositionFree_DI (Local_Digital_IO · %IX0.7) | Config: GVL_Config</t>
+          <t>Variateur AC600 ➔ Afficheur de façade (Attendu : état 'rdy' ou fréquence 0.0) | Câble RJ45 EtherCAT Port IN</t>
         </is>
       </c>
       <c r="J247" s="3" t="inlineStr">
@@ -12256,7 +13108,7 @@
         </is>
       </c>
       <c r="K269" s="3" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270">
@@ -12299,7 +13151,7 @@
         </is>
       </c>
       <c r="K270" s="2" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="271">
@@ -12342,7 +13194,7 @@
         </is>
       </c>
       <c r="K271" s="3" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="272">
@@ -12514,7 +13366,7 @@
         </is>
       </c>
       <c r="K275" s="3" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="276">
@@ -12557,7 +13409,7 @@
         </is>
       </c>
       <c r="K276" s="2" t="n">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="277">
@@ -12600,7 +13452,7 @@
         </is>
       </c>
       <c r="K277" s="3" t="n">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="278">
@@ -12643,7 +13495,7 @@
         </is>
       </c>
       <c r="K278" s="2" t="n">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="279">
@@ -12686,7 +13538,7 @@
         </is>
       </c>
       <c r="K279" s="3" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="280">
@@ -12729,7 +13581,7 @@
         </is>
       </c>
       <c r="K280" s="2" t="n">
-        <v>433</v>
+        <v>448</v>
       </c>
     </row>
     <row r="281">
@@ -12772,7 +13624,7 @@
         </is>
       </c>
       <c r="K281" s="3" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="282">
@@ -12815,7 +13667,7 @@
         </is>
       </c>
       <c r="K282" s="2" t="n">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="283">
@@ -12858,7 +13710,7 @@
         </is>
       </c>
       <c r="K283" s="3" t="n">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="284">
@@ -12901,7 +13753,7 @@
         </is>
       </c>
       <c r="K284" s="2" t="n">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="285">
@@ -12944,7 +13796,7 @@
         </is>
       </c>
       <c r="K285" s="3" t="n">
-        <v>473</v>
+        <v>488</v>
       </c>
     </row>
     <row r="286">
@@ -12987,7 +13839,7 @@
         </is>
       </c>
       <c r="K286" s="2" t="n">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -13011,9 +13863,9 @@
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -13103,12 +13955,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NOT LocalIoValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication interne ou panne matérielle du module CPU Local_Digital_IO (Slot 1).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper la commande au pupitre. Noter le code ALM_001.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier voyant ERR/RUN sur la CPU VEICHI. Contrôler alimentation 24Vcc et connectique nappe de fond de panier.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 1 Local_Digital_IO ➔ Voyants CPU : RUN Vert fixe, ERR Éteint ➔ Mesure : 24Vcc entre bornes +24V et 0V</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13146,12 +14010,24 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>NOT Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+          <t>🔌 Défaut de communication coupleur ou coupure 24V sur le module d'entrées VH_0800END (Slot 3).</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Couper les commandes au pupitre. Verrouiller le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier clip de verrouillage fond de panier Slot 3. Mesurer alimentation 24Vcc sur le bornier du module VH_0800END.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 3 VH_0800END ➔ Mesure : 24Vcc sur bornes d'alimentation module ➔ LED PWR allumée verte</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13189,12 +14065,24 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NOT Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication ou panne d'alimentation du module mixte VH_0808ETP (Slot 2).</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Interdiction translation et treuils au pupitre. Relever le code ALM_003.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler enfichage Slot 2 sur le rail DIN. Vérifier fusible protection 24Vcc de la carte VH_0808ETP.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 2 VH_0808ETP ➔ Mesure : 24Vcc sur bornes d'alimentation carte ➔ LED PWR allumée verte</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13232,12 +14120,24 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>NOT Vh0008ErValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+          <t>🔌 Défaut d'alimentation ou défaillance du module 8 sorties relais VH_0008ER (Slot 4 - Freins).</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Interdiction des commandes treuils et translation au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier module Slot 4. Contrôler présence du 24Vcc sur les communs relais C0..C7 et la nappe interne.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 4 VH_0008ER ➔ Mesure : 24Vcc sur communs relais ➔ Vérifier étrier fond de panier bien enclenché</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13275,12 +14175,24 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NOT Vh0008Er1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>🔌 Défaut de communication ou d'alimentation du module sorties relais VH_0008ER_1 (Slot 5 - Sécurité).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Frapper l'arrêt d'urgence au pupitre. Condamner le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier Slot 5. Contrôler alimentation 24Vcc et boucle de maintien puissance PowerKeepAlive.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Automate VEICHI · Slot 5 VH_0008ER_1 ➔ Mesure : 24Vcc sur communs C6/C7 (%QX28.6/%QX28.7) ➔ Attendu : Relais fermés au réarmement puissance</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13318,12 +14230,24 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NOT CanBusValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+          <t>📡 Défaillance générale du bus CANopen maître CPU (câble blindé coupé, parasite sévère, bus éteint).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes. Couper puis réenclencher l'alimentation générale du pupitre.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier résistance 120 Ω à chaque extrémité du bus CAN. Contrôler le blindage et la continuité des lignes CAN_H et CAN_L.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Port CANopen CPU VEICHI ➔ Mesure hors tension : 60 Ω entre CAN_H et CAN_L ➔ Sous tension : ~2.5Vcc sur CAN_H et CAN_L par rapport au 0V</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13361,12 +14285,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CanBusValid AND NOT Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>📡 Joystick pupitre JOY1 non détecté sur le bus CANopen (Node ID 1 absent ou 24V pupitre coupé).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre le joystick physique au neutre mécanique. Couper et réarmer le commutateur pupitre.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler 24Vcc sur connecteur JOY1 sous pupitre. Vérifier l'état de la LED CANopen sous le manipulateur (Verte clignotante = Pre-Op).</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Connecteur JOY1 sous pupitre ➔ Mesure : 24Vcc entre broche 1 (+) et broche 2 (0V) ➔ Câble CAN blindé 2 paires</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13404,12 +14340,24 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>NOT EcatBusValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>📡 Rupture de communication sur le maître EtherCAT automate (câble principal débranché ou perturbation CEM).</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes machine. Noter code ALM_008 au pupitre.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : inspecter câble Ethernet blindé RJ45 partant du port EtherCAT CPU vers le premier esclave (variateur AC600).</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Port EtherCAT CPU VEICHI ➔ LED Link/Act : Verte clignotante (trafic actif) ➔ Cordon Ethernet industriel blindé CAT5e/CAT6</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13447,12 +14395,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>📡 Codeur absolu COD1 treuil levage M1 non détecté sur le bus EtherCAT (câble touret M12 coupé ou 24V manquant).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer le treuil M1. Rester au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Treuil M1 : contrôler voyants LED (PWR, L/A) sur connecteur M12 du codeur COD1. Tester continuité des 4 paires du cordon en chaîne porte-câbles.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD1 (Treuil M1) ➔ Port M12 IN ➔ Attendu : 24Vcc broches 1-3, LED L/A Verte clignotante</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13490,12 +14450,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+          <t>📡 Codeur absolu COD2 treuil benne M2 non détecté sur le bus EtherCAT (câble touret M12 coupé ou 24V manquant).</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer le treuil M2. Rester au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Treuil M2 : contrôler voyants LED (PWR, L/A) sur connecteur M12 du codeur COD2. Tester cordon chaîne porte-câbles et disjoncteur 24V capteurs.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD2 (Treuil M2) ➔ Port M12 IN ➔ Attendu : 24Vcc broches 1-3, LED L/A Verte clignotante</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13533,12 +14505,24 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>EcatBusValid AND NOT VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>📡 Variateur translation AC600 non détecté sur le bus EtherCAT (drive éteint ou câble RJ45 déconnecté).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Translation M3 immobilisée. Ne pas insister sur les commandes.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier disjoncteur alimentation Q_Drive variateur. Contrôler voyant LINK sur port RJ45 EtherCAT du drive AC600.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Variateur AC600 ➔ Port RJ45 EtherCAT IN ➔ Attendu : LED Link verte fixe/clignotante ➔ Disjoncteur drive enclenché</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13576,12 +14560,24 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication avec le pupitre ou heartbeat IHM interrompu pendant la commande de levage M1.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre les manipulateurs au neutre au pupitre. Vérifier l'écran IHM.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le réseau Ethernet IHM-PLC et l'alimentation 24V de la dalle tactile de supervision.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Port Ethernet IHM ➔ Ping IP automate VEICHI ➔ Diagnostic variable GVL_IHM.Commun.HeartbeatIhmOk</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13619,12 +14615,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorEncoder AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>📡 Perte de signal ou anomalie trame du codeur treuil M1 en mouvement (perte comptage position).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt du treuil M1. Ne pas passer en mode automatique. Mettre au neutre.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier fixation mécanique de l'axe codeur COD1 sur le tambour treuil M1. Contrôler connecteur M12 et blindage.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Variable PRG_02_Acquisition.Data.EncoderM1.Measurement.EncoderAvailable ➔ Attendu : TRUE</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13662,12 +14670,24 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+          <t>⚡ Détection d'une inversion de phase 400V ou coupure de phase pendant l'exploitation du treuil M1.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper les commandes au pupitre.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le relais de surveillance des phases en armoire tête. Mesurer tension 400Vac entre phases L1, L2, L3.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal ➔ 0V si défaut phase</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13705,12 +14725,24 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaA AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>🚨 Dérive non commandée M1 (Meca A) : rotation du tambour détectée &gt; 5.0m alors que les commandes et le frein sont coupés.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>🛑 NE TOUCHER À RIEN. Enclencher l'Arrêt d'Urgence coup de poing pupitre si le tambour continue de tourner sous la charge.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER GRAVITATIONNEL : Interdire l'accès sous la flèche. Armoire : mesurer 0V sur bobine frein M1. Remplacer les garnitures si patinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>VH_0008ER · %QX27.0 = 0 | VH_0800END · %IX225.0 = 0V ➔ Mesure bornier frein treuil M1 : 0V strict</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13748,12 +14780,24 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaB AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt M1 (Meca B) : contacteurs ou frein restés enclenchés &gt; 3s après retour au neutre du manipulateur.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur M1 au neutre. Contrôler visuellement l'arrêt complet du tambour treuil.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier si contacteur KM_M1 ou relais de défreinage reste mécaniquement coincé fermé. Contrôler varistance anti-arc.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · %IX0.0 (M1_ContactorsReleased_DI) ➔ Attendu repos : 24V | VH_0800END · %IX225.0 (BrakeOpen) ➔ Attendu repos : 0V</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13791,12 +14835,24 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaC AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>🚨 Glissement M1 pendant cycle benne (Meca C) : le treuil M1 a dérivé de plus de 2.0m alors qu'il devait maintenir la charge immobile.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de l'action benne. Mettre les manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le couple de serrage du frein treuil M1. Vérifier si la bobine de défreinage M1 n'a pas reçu d'alimentation parasite.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Mesure multimètre DC aux bornes bobine frein M1 pendant fermeture benne : 0V strict ➔ MecaCDriftM &gt; 2.0m</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13834,12 +14890,24 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaD AND LocalIoValid AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+          <t>🚨 Non-arrêt capteur haut M1 (Meca D) : le treuil a franchi le fin de course haut sans que l'arrêt ne soit confirmé sous 3s.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>🛑 ARRÊT IMMÉDIAT. Ne pas tenter de forcer la montée. Vérifier que la tête de flèche n'est pas en butée.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler détecteur inductif fin de course haut M1M2_TopPositionFree_DI (%IX0.7). Vérifier la chaîne de coupure contacteurs montée.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.7 (M1M2_TopPositionFree_DI) ➔ Attendu libre : 24V (Contact NC) | Ouvert en butée : 0V</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13877,12 +14945,24 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorMecaE AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>🚨 Écart critique synchronisation M1/M2 (Meca E) : décalage entre câbles &gt; 7.0m en mouvement couplé solidaire.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre. Vérifier visuellement l'assiette et le comportement de la benne.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Relever positions codeurs M1 et M2 sur l'IHM. Vérifier si un tambour patine ou si un câble a sauté d'une gorge.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>IHM Synchro ➔ Écart brut ABS(CablePosM1 - CablePosM2 + ActiveOffsetM) &gt; 7.0m ➔ TonMecaE = 3s avant coupure puissance</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13920,12 +15000,24 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOppositeDir AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+          <t>🚨 Sens de rotation opposé M1 : le tambour tourne à l'envers de la commande demandée au manipulateur pendant plus de 1s.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener le manipulateur au neutre au pupitre. Ne pas forcer la commande.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'ordre des phases moteur sur contacteurs montée/descente KM1/KM2 en armoire. Vérifier polarité de comptage codeur COD1.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Mesure : Vitesse signée SignedSpeed_Mps ➔ Attendu : Même polarité que l'ordre RelayFwd/RelayRev</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -13953,7 +15045,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>[M1] ErrorID:16 - absence mouvement</t>
+          <t>[M1] ErrorID:16 - discordance commande/retour/mouvement</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -13963,12 +15055,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorNoMovement AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>⏱️ Absence de mouvement M1 : commande active et freins ouverts mais aucune progression de câble mesurée après 3s.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre. Vérifier visuellement si le câble ou le tambour est bloqué mécaniquement.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier disjoncteur moteur Q_M1 et présence tension 400Vac en sortie contacteurs de sens. Contrôler décollement mécanique frein.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.1 (M1_ThermalOk_DI) ➔ Mesure : 400Vac bornes moteur ➔ Attendu repos : 24Vcc sur %IX0.1 et 400Vac en commande</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14006,12 +15110,24 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>WinchM1Safety.ErrorOverspeed AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+          <t>⚠️ Survitesse treuil M1 détectée par le codeur COD1 au-delà de la bande maximale autorisée (SafeStop déclenché).</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur M1 au neutre. Laisser le treuil s'immobiliser sous rampe contrôlée.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'accouplement mécanique du codeur COD1. Vérifier si la charge n'entraîne pas le tambour au-delà de la vitesse nominale.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM ➔ Vitesse mesurée Speed_Mps &gt; SpeedBandMaxMps[5] ➔ SafeStop actif sans PowerCutOff</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14049,12 +15165,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>📡 Perte de communication opérateur ou coupure heartbeat IHM pendant la commande du treuil benne M2.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur benne au neutre au pupitre. Contrôler l'écran tactile.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le commutateur pupitre et la liaison Ethernet IHM-automate.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Port Ethernet IHM ➔ Ping IP automate VEICHI ➔ GVL_IHM.Commun.HeartbeatIhmOk</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14092,12 +15220,24 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorEncoder AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+          <t>📡 Perte de signal ou défaut de mesure du codeur absolu treuil M2 COD2.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des manœuvres benne. Manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le câble blindé M12 et la fixation de l'axe codeur COD2 sur le tambour M2.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD2 Treuil M2 ➔ Variable PRG_02_Acquisition.Data.EncoderM2.Measurement.EncoderAvailable ➔ Attendu : TRUE</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14135,12 +15275,24 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>⚡ Inversion ou coupure d'une phase réseau 400V pendant l'exploitation du treuil benne M2.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine. Couper les commandes au pupitre.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler le relais de surveillance des phases en armoire tête. Mesurer tension triphasée 400Vac.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14178,12 +15330,24 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaA AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
+          <t>🚨 Dérive non commandée M2 (Meca A) : rotation du tambour treuil benne &gt; 5.0m sans commande active.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>🛑 NE TOUCHER À RIEN. Enclencher l'Arrêt d'Urgence pupitre si la benne descend toute seule.</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER : Condamner le pupitre. Armoire : mesurer 0V sur bobine frein M2. Remplacer les garnitures si patinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>VH_0008ER · %QX27.1 = 0 | VH_0800END · %IX225.1 = 0V ➔ Mesure bornier frein treuil M2 : 0V strict</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14221,12 +15385,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaB AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt M2 (Meca B) : contacteurs ou frein M2 restés enclenchés &gt; 3s après retour au neutre.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur benne au neutre. Contrôler l'arrêt complet du tambour treuil M2.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler retombée mécanique du contacteur KM_M2 et relais frein. Remplacer si contacts collés.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · %IX0.2 (M2_ContactorsReleased_DI) ➔ Attendu repos : 24V | VH_0800END · %IX225.1 (BrakeOpen) ➔ Attendu : 0V</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14264,12 +15440,24 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaC AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
+          <t>🚨 Glissement M2 pendant benne figée (Meca C) : dérive anormale du tambour benne M2.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la manœuvre. Mettre les manipulateurs au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier étanchéité et réglage entrefer frein M2. Mesurer absence de tension sur bobine frein M2.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Bornier frein treuil M2 ➔ Mesure : Tension bobine frein ➔ Attendu : 0Vcc et dérive MecaCDriftM &lt; 2.0m</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14307,12 +15495,24 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaD AND LocalIoValid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>🚨 Non-arrêt capteur haut M2 (Meca D) : treuil benne ayant dépassé le fin de course haut sans s'arrêter sous 3s.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>🛑 ARRÊT IMMÉDIAT. Ne pas forcer la montée. Vérifier que le câble n'est pas en butée contre le tambour.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler détecteur inductif fin de course haut M1M2_TopPositionFree_DI (%IX0.7) et contacteurs montée M2.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.7 (M1M2_TopPositionFree_DI) ➔ Attendu libre : 24V | Ouvert : 0V</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14350,12 +15550,24 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorMecaE AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
+          <t>🚨 Écart critique synchronisation M2/M1 (Meca E) : dérive différentielle des treuils &gt; 7.0m en marche couplée.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre. Vérifier l'état visuel des câbles sur le ponton.</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler valeurs de position COD1 et COD2 sur IHM. Vérifier absence de glissement câble dans les tambours.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM Synchro ➔ Écart absolu &gt; 7.0m ➔ TonMecaE = 3s avant coupure puissance</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14393,12 +15605,24 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOppositeDir AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>🚨 Sens de rotation opposé M2 : rotation du tambour à l'envers de la commande demandée pendant plus de 1s.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler câblage phases puissance moteur M2 sur contacteurs KM_M2. Vérifier sens comptage codeur COD2.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Codeur COD2 Treuil M2 ➔ Mesure : Vitesse signée SignedSpeed_Mps ➔ Attendu : Même polarité que l'ordre RelayFwd/RelayRev</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14426,7 +15650,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>[M2] ErrorID:16 - absence mouvement</t>
+          <t>[M2] ErrorID:16 - discordance commande/retour/mouvement</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -14436,12 +15660,24 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorNoMovement AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr"/>
+          <t>⏱️ Absence de mouvement M2 : commande active et frein ouvert mais aucune rotation mesurée après 3s.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur au neutre. Contrôler visuellement si la benne ou le tambour est coincé.</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : contrôler disjoncteur moteur Q_M2 et présence 400Vac aux bornes moteur. Contrôler défreinage mécanique.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.3 (M2_ThermalOk_DI) ➔ Mesure : 400Vac bornes moteur ➔ Attendu repos : 24Vcc sur %IX0.3 et 400Vac en commande</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14479,12 +15715,24 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>WinchM2Safety.ErrorOverspeed AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>⚠️ Survitesse treuil M2 détectée par codeur COD2 au-delà du palier 5 (SafeStop activé).</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur benne au neutre. Attendre l'arrêt complet sous rampe.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler l'accouplement du codeur COD2. Vérifier absence d'emballement sous le poids de la benne.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic IHM ➔ Vitesse mesurée Speed_Mps &gt; SpeedBandMaxMps[5] ➔ SafeStop actif</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14522,12 +15770,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorOperatorComm AND Joy1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication opérateur pupitre pendant la commande de translation portique M3.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre le manipulateur translation au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler bus CANopen JOY1 et heartbeat supervision IHM.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Bus CANopen Pupitre ➔ Diagnostic trames CAN ➔ Attendu : NMT Operational et HeartbeatIhmOk = TRUE</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14565,12 +15825,24 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorDriveComm AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>📡 Perte de communication bus EtherCAT avec le variateur translation VEICHI AC600.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Translation bloquée. Mettre les commandes au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler cordon RJ45 EtherCAT reliant l'automate au variateur AC600. Vérifier alimentation commande drive.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Variateur AC600 ➔ Port EtherCAT IN ➔ Attendu : Câble RJ45 connecté, LED Link/Act verte clignotante</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14608,12 +15880,24 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorPhaseRotation AND Vh0800Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
+          <t>⚡ Rotation de phase 400V incorrecte ou perte de phase sur l'alimentation de la translation.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt immédiat de la machine au pupitre.</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier relais de phases et tension 400Vac en amont du variateur AC600.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Attendu : 24Vcc normal</t>
+        </is>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14651,12 +15935,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorMecaB AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
+          <t>⏱️ Absence confirmation arrêt translation (Meca B) : variateur ou frein M3 toujours actifs &gt; 3s après stop.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre. Vérifier visuellement l'immobilisation du portique.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier contacteur frein translation KM_Frein_M3 et sortie fréquence variateur AC600.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Borne %IX225.2 (M3_BrakeIsOpen_DI) ➔ Attendu arrêt : 0V | Variateur AC600 : Fréquence &lt; 0.5 Hz</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14694,12 +15990,24 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorMecaA AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
+          <t>🚨 Mouvement non commandé translation (Meca A) : déplacement portique détecté sans consigne active après 1s.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Frapper l'Arrêt d'Urgence pupitre si le portique dérive le long des rails sous l'effet du vent.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER : Condamner le portique avec cales rail. Armoire : mesurer 0V sur bobine frein translation. Remplacer patins de frein si usés.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Bornier armoire frein M3 ➔ Mesure : 0V strict ➔ Variateur AC600 : Fréquence mesurée &gt; 0.5 Hz sans commande</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14737,12 +16045,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorLimitSwitch AND Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+          <t>🚨 Fin de course extrême translation actionné (dépassement zone Trémie ou Maintenance).</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne plus avancer vers la butée. Passer en dérogation au pupitre pour reculer hors de la zone.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier palpeur inductif came extrême sur voie de roulement. Contrôler boîte de raccordement chariot.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Borne %IX224.0 (Trémie) ou %IX224.4 (Maintenance) ➔ Mesure : 24Vcc sur la came concernée</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14780,12 +16100,24 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>TranslationSafety.ErrorSensorIncoherent AND Vh0808Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+          <t>📐 Combinaison de cames translation physiquement impossible (ex: Trémie et Maintenance actives en même temps).</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt des commandes translation au pupitre. Relever la position visuelle approximative du portique.</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Inspecter les 5 capteurs inductifs de cames translation le long des rails (boue, graviers, câbles blessés).</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Bornes %IX224.0 à %IX224.4 ➔ Mesure 24Vcc : Une seule came active autorisée à la fois</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14823,12 +16155,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>⚡ Défaut séquence / retour frein translation M3 (discordance entre ordre défreinage et recopie armoire).</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : tester contacteur relais frein KM_Frein_M3. Mesurer tension bobine défreinage en manœuvre.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>VH_0008ER · Relais %QX27.2 (Cmd) vs VH_0800END · Borne %IX225.2 (Retour %IX225.2) ➔ Concordance exigée sous 500 ms</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14866,12 +16210,24 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0008) &lt;&gt; 16#0000) AND VarM3Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+          <t>⚡ Défaut variateur translation AC600 (surcharge, surintensité, sous-tension bus continu ou défaut thermique).</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateur translation au neutre au pupitre. Patienter 5 min pour refroidissement.</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : relever le code affiché sur le bandeau digital du variateur AC600 (ex: E.OC, E.OL, E.LU). Contrôler résistance de freinage.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Afficheur variateur AC600 ➔ Code défaut | Mesure bus DC : ~560Vcc entre bornes (+) et (-)</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14909,12 +16265,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>((TranslationMotionErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>🛑 Butée mécanique finale de translation atteinte (arrêt immédiat sur bordure de voie).</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser le manipulateur pour dégager le portique en sens inverse.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler amortisseurs de fin de course rail et état mécanique du linguet de déclenchement.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>VH_0808ETP · Bornes %IX224.0 ou %IX224.4 ➔ Mesure : 24Vcc entre borne et 0V ➔ Attendu hors butée : 0V (Détecteur inductif NO libre)</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14952,12 +16320,24 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>(TranslationFinalInterlockErrorId &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr"/>
+          <t>🔒 Barrière finale translation active : interlock frein ou redémarrage engagé nécessitant un acquittement explicite.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener le manipulateur au neutre. Appuyer sur le bouton Acquittement / Reset au pupitre.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier mot d'état TranslationFinalInterlockErrorId sur l'écran de diagnostic IHM.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Pupitre / IHM ➔ Diagnostic variable TranslationFinalInterlockErrorId ➔ Attendu : Valeur 0 après front montant bouton Reset</t>
+        </is>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -14995,12 +16375,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>⚙️ Configuration géométrie benne invalide (offset fermé inférieur ou égal à l'offset ouvert en mémoire).</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Ne pas tenter de manœuvrer la benne au pupitre.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>💻 IHM Réglages : vérifier paramètres géométrie benne. L'offset fermé doit être supérieur à l'offset ouvert (nominal 15.0m &gt; 0.0m).</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>IHM Réglages Benne ➔ Variables OffsetCloseM vs OffsetOpenM ➔ Attendu : OffsetCloseM (nom. 15.0m) strictement supérieur à OffsetOpenM (0.0m)</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15038,12 +16430,24 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr"/>
+          <t>🪣 Dépassement écart maximum autorisé benne : décalage M2 - M1 hors plage physique plausible (&gt; 17m ou &lt; -1m).</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Passer en mode Manuel Dérogation : ramener visuellement la benne dans une position intermédiaire normale.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier position codeurs M1 et M2. Vérifier absence de glissement de câble ou de mou exagéré.</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>IHM Benne ➔ Écart mesuré CablePosM2 - CablePosM1 ➔ Attendu : Compris dans l'intervalle [-1.0m .. 17.0m]</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15081,12 +16485,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0004) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout déplacement benne : la benne n'a pas atteint sa position ouverte ou fermée sous 60 secondes.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre. Vérifier visuellement si la benne est coincée dans le matériau.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler vitesse treuil M2 et état mécanique des poulies de fermeture benne.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Bloc FB_Bucket ➔ Temporisateur interne TonTimeout ➔ Attendu : Temps écoulé ET &lt; CfgTimeoutDuration (T#60s)</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15124,12 +16540,24 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
+          <t>🚨 Glissement treuil M1 détecté pendant manœuvre benne (&gt; 1.0m de mouvement flèche non autorisé).</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Arrêt de la commande benne. Ramener au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler frein treuil M1 et absence de rotation parasite pendant l'actionnement du treuil M2.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Treuil M1 ➔ Écart position ABS(CablePosM1 - M1RefPosM) ➔ Attendu : Dérive &lt; 1.0m pendant manœuvre benne</t>
+        </is>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15167,12 +16595,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>((BucketErrorId AND 16#0010) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>📍 Codeurs treuils non référencés pour la séquence benne (homing machine non validé après mise sous tension).</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Effectuer la procédure de référencement machine (Homing) au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>💻 Vérifier drapeaux HomedM1 et HomedM2 sur la page diagnostic superviseur.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Supervision IHM / PLC ➔ Variables HomedAndReliableM1 et HomedAndReliableM2 ➔ Attendu : État TRUE sur les deux axes</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15210,12 +16650,24 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>((SyncErrorId AND 16#0001) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
+          <t>⚠️ Écart de synchronisation M1/M2 supérieur à 6.0m en marche couplée (SafeStop activé).</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre. Vérifier visuellement la planéité des câbles.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler vitesse respective des tambours M1 et M2. Recaler l'assiette en pilotage unitaire si nécessaire.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>FB_SyncDeviation ➔ Écart calculé DeltaPosM ➔ Attendu : DeltaPosM &lt; 6.0m (seuil d'arrêt)</t>
+        </is>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15253,12 +16705,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>((SyncErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>🔀 Discordance contacteurs M1/M2 en marche synchronisée (un treuil commandé et pas l'autre ou paliers différents).</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Manipulateurs au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier la chaîne de commande des contacteurs de sens et paliers M1 et M2. Contrôler relais de sortie.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>FB_SyncContactor ➔ Variable ContactorMismatch ➔ Attendu repos / marche couplée : FALSE (Vecteurs identiques)</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15296,12 +16760,24 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr"/>
+          <t>⏱️ Timeout immersion cycle automatique : temps d'atteinte de la surface d'eau dépassé.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en mode Manuel au pupitre. Remonter la benne en surface.</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier réglage altimétrique du plan d'eau (ImmersionUpper_M) sur l'IHM cycle.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Bloc FB_CycleSemiAuto ➔ Temporisateur phase plongée ➔ Attendu : Atteinte plan d'eau avant expiration T#Timeout</t>
+        </is>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15339,12 +16815,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout détection fond : la benne descend sous l'eau sans toucher le fond dans le temps alloué.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Stopper la descente automatique. Repasser en manuel au pupitre.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler fonctionnement palpeur Kobold ou seuil altimétrique de profondeur fond.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Bloc FB_CycleSemiAuto ➔ Temporisateur descente fond ➔ Attendu : Contact fond avant seuil temps alloué</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15382,12 +16870,24 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0004) &lt;&gt; 16#0000) AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
+          <t>🛑 Limite basse de plongée atteinte : la benne a atteint la profondeur maximale autorisée.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser la commande pour remonter la benne au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier seuil de profondeur légale CfgCableLimitDescentM sur la page configuration IHM.</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Codeur COD1 Treuil M1 ➔ Variable CablePosM1 ➔ Attendu : Position supérieure à CfgCableLimitDescentM (-50.0m)</t>
+        </is>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15425,12 +16925,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>🌊 Contact fond perdu pendant l'extraction (glissement de la benne dans la boue ou perte signal Kobold).</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Arrêter la montée rapide. Passer en manuel lent pour assurer la fermeture.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler capteur palpeur Kobold (%IX0.5) et liaison électrique touret.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.5 (KoboldBottomTouch_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu : 24V reposée au fond (0V en suspension)</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15468,12 +16980,24 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0010) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
+          <t>🪢 Perte tension câble benne M2 sous l'eau (mou de câble détecté par la roulette palpeuse).</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Passer en manuel dérogation au pupitre : retendre doucement le câble M2.</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier mécanique bras palpeur anti-mou sur tambour M2 et propreté de l'interrupteur.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.4 (M2_TensionedCable_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu câble tendu : 24V (Contact NC fermé)</t>
+        </is>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15511,12 +17035,24 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0020) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>⚠️ Anomalie de vitesse treuils pendant la phase de plongée (dérive d'accélération sous l'eau).</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener commandes au neutre au pupitre. Laisser la charge se stabiliser.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler régularité vitesse codeurs M1 et M2 en plongée.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Codeurs COD1/COD2 ➔ Dérivée d(Speed_Mps)/dt en plongée ➔ Attendu : Accélération stable dans le gabarit défini</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15554,12 +17090,24 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>((DiveErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="3" t="inlineStr"/>
+          <t>⚙️ Configuration de plongée invalide (paramètres altimétriques immersion / fond incohérents).</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Cycle semi-auto refusé. Relever paramètres IHM au pupitre.</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier cohérence paramètres cycle plongée sur le superviseur.</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>IHM Recettes Dragage ➔ Variables GVL_IHM.CycleSemiAuto.Cfg ➔ Attendu : Cohérence altimétrique Fond &lt; Immersion &lt; Crête</t>
+        </is>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15597,12 +17145,24 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0001) &lt;&gt; 16#0000) AND LocalIoValid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>🌊 Défaut contact fond pendant la phase d'extraction des matériaux.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en manuel au pupitre. Vérifier tension des câbles.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler capteur de fond et seuil d'effort sur treuils.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Local_Digital_IO · Borne %IX0.5 (KoboldBottomTouch_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu : 24V au fond</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15640,12 +17200,24 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr"/>
+          <t>🪣 Défaut fermeture benne pendant l'extraction (benne n'atteignant pas l'état fermé sous l'eau).</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en commande manuelle benne M2 pour forcer la fermeture au pupitre.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler absence d'enrochement coincé dans les mâchoires de la benne.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Supervision IHM ➔ Variable _BucketState.IsClosed ➔ Attendu : Confirmation TRUE sous 60s max</t>
+        </is>
+      </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15683,12 +17255,24 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0004) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>⏱️ Défaut contrôle vitesse montée lors de l'extraction initiale (distance de contrôle non franchie).</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener manipulateur au neutre au pupitre.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Vérifier passage au palier 1 pendant la traversée de la zone ExtractionControlDistance_M.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Contacteurs Paliers Vitesse ➔ Relais palier 1 KM_P1 (%QX27.4) ➔ Attendu : Enclenchement exclusif du Palier 1 dans zone décollement</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15726,12 +17310,24 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>((ExtractionErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr"/>
+          <t>⚙️ Configuration extraction cycle automatique invalide.</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Bloquer cycle auto au pupitre.</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>💻 Revoir paramètres de la phase extraction sur l'écran IHM.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>IHM Recettes Dragage ➔ Variables GVL_IHM.CycleSemiAuto.Cfg ➔ Attendu : Cohérence paramètres d'extraction</t>
+        </is>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15769,12 +17365,24 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0001) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>🚨 Discordance redondance contacteurs de puissance ligne ou relais de sécurité AU (contact miroir non retombé).</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>🛑 COUPURE GÉNÉRALE. Frapper coup de poing Arrêt d'Urgence pupitre. Condamner le poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ DANGER DE MORT 400V : Consigner la source quai/groupe + VAT. Contrôler les contacts miroirs NC du contacteur de ligne KM_Power et blocs auxiliaires de sécurité.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>VH_0800END · Bornes %IX225.6 et %IX225.7 ➔ Mesure : 24Vcc / 0V entre bornes et 0V carte ➔ Attendu réarmé : 24Vcc sur les deux voies</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15812,12 +17420,24 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0002) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
+          <t>🚨 Échec confirmation armement puissance (le contacteur de ligne ne s'enclenche pas sous 2s après commande).</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Relâcher le bouton Réarmement. Vérifier que tous les AU sont déverrouillés au pupitre.</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Armoire : vérifier bobine contacteur ligne KM_Power, fusible commande 24V et module sécurité AU.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>VH_0008ER_1 · Relais %QX28.6/%QX28.7 (PowerKeepAlive) ➔ Mesure : 24Vcc sur bobine KM_Power ➔ Attendu : 24Vcc après appui réarmement</t>
+        </is>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15855,12 +17475,24 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>((EmergencyErrorId AND 16#0008) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>🚨 Échec autotest démarrage chaîne d'urgence (défaut de retombée d'un canal lors du test d'initialisation).</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>🛑 Redémarrage puissance refusé. Condamner le pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler les contacts de recopie de tous les relais de sécurité en armoire électrique.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Bloc Sécurité FB_Safety_EmergencyManagement ➔ Contrôle retombée des canaux d'urgence ➔ Attendu : 0V strict sur toutes les lignes avant réarmement</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15898,12 +17530,24 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0001) &lt;&gt; 16#0000) AND EncM1Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>🛑 Profondeur limite légale atteinte en cycle automatique (arrêt fond de fouille autorisé).</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Inverser les commandes au pupitre pour remonter la benne. Ne pas descendre plus bas.</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>💻 Vérifier valeur de la limite légale autorisée sur l'écran réglages IHM.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>IHM Configuration Cycle ➔ Variable CablePosM1 vs LimitLegalDepthMinAllowed_M ➔ Attendu : CablePosM1 supérieur à la limite légale</t>
+        </is>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15941,12 +17585,24 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0002) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>⚠️ Défaut de synchronisation des treuils en cours de cycle automatique.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Stopper le cycle semi-auto au pupitre. Repasser en manuel.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler équilibrage de charge et vitesses relatives M1/M2.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Supervision Cycle ➔ Mot CycleErrorId bit 1 ➔ Attendu : Écart M1/M2 dans le gabarit cycle semi-auto</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -15984,12 +17640,24 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0008) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="3" t="inlineStr"/>
+          <t>⚠️ Écart codeurs excessif constaté pendant la phase de remontée de charge.</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>🕹️ Ramener commandes au neutre au pupitre. Vérifier assiette benne.</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler absence de glissement mécanique sur l'un des deux tambours de treuil.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Codeurs COD1/COD2 ➔ Mot CycleErrorId bit 3 ➔ Attendu : Écart codeurs en montée inférieur au seuil critique</t>
+        </is>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -16027,12 +17695,24 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0010) &lt;&gt; 16#0000) AND EncM1Valid AND EncM2Valid AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>⚠️ Écart de vitesse confirmé entre treuils M1 et M2 en déplacement couplé.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Mettre les manipulateurs au neutre au pupitre de commande.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler contacteurs de paliers de vitesse en armoire (KM_P1 à KM_P5).</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Supervision Moteurs ➔ Mot CycleErrorId bit 4 ➔ Attendu : Concordance des vitesses treuils en marche couplée</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -16070,12 +17750,24 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0020) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr"/>
+          <t>📡 Perte de communication avec le pupitre IHM pendant le déroulement d'un cycle automatique.</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>🛑 Le cycle s'interrompt en sécurité. Vérifier l'écran IHM au poste de conduite.</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>🧰 Contrôler câble réseau Ethernet blindé et switch réseau armoire.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Liaison Ethernet IHM ➔ Mot CycleErrorId bit 5 ➔ Attendu : HeartbeatIhmOk maintenu actif en continu</t>
+        </is>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -16113,12 +17805,24 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>((CycleErrorId AND 16#0040) &lt;&gt; 16#0000) AND (AlarmCount &lt; CST_NbMaxAlarmes)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>⏱️ Timeout d'étape cycle automatique : l'étape active du cycle a dépassé sa durée maximale allouée.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>🕹️ Repasser en mode Manuel au pupitre de commande. Dégager la machine si nécessaire.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>💻 Contrôler le numéro d'étape bloquée E_AutoCycleStep sur la page de supervision.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>FB_CycleSemiAuto ➔ Temporisateur d'étape active ➔ Attendu : Transition d'étape accomplie avant expiration timeout</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
           <t>FB_Hmi_BannerFormatter.st</t>
@@ -23253,17 +24957,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Mettre les manipulateurs treuils au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre les manipulateurs au neutre sur le pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>🧰 Tester le contacteur frein M1 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts collés.</t>
+          <t>🧰 Tester le contacteur frein KM_Frein_M1 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Cmd: M1_BrakeRelease_RQ (VH_0008ER · %QX27.0) | Retour: M1_BrakeIsOpen_DI (VH_0800END · %IX225.0)</t>
+          <t>VH_0008ER · Relais %QX27.0 (M1_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C0/NO0 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.0 (M1_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -23308,17 +25012,17 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Mettre le manipulateur benne au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre le manipulateur benne au neutre au pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>🧰 Tester le contacteur frein M2 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
+          <t>🧰 Tester le contacteur frein KM_Frein_M2 en armoire. Mesurer 0V sur la bobine de défreinage à l'arrêt. Remplacer si contacts soudés.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Cmd: M2_BrakeRelease_RQ (VH_0008ER · %QX27.1) | Retour: M2_BrakeIsOpen_DI (VH_0800END · %IX225.1)</t>
+          <t>VH_0008ER · Relais %QX27.1 (M2_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C1/NO1 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.1 (M2_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -23363,17 +25067,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Mettre le manipulateur translation au neutre. Relancer le Preflight.</t>
+          <t>🕹️ Mettre le manipulateur translation au neutre au pupitre. Relancer le Preflight.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le relais/contacteur frein M3 en armoire. Mesurer 0V sur la bobine à l'arrêt.</t>
+          <t>🧰 Contrôler le relais frein KM_Frein_M3 en armoire. Mesurer 0V sur la bobine à l'arrêt.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Cmd: M3_BrakeRelease_RQ (VH_0008ER · %QX27.2) | Retour: M3_BrakeIsOpen_DI (VH_0800END · %IX225.2)</t>
+          <t>VH_0008ER · Relais %QX27.2 (M3_BrakeRelease_RQ) ➔ Mesure : Continuité contact sec C2/NO2 ➔ Attendu repos : 0V / Contact ouvert | VH_0800END · Borne %IX225.2 (M3_BrakeIsOpen_DI) ➔ Attendu repos : 0V</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -23413,22 +25117,22 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>🚨 Contacteur de puissance sens/vitesse M1 resté collé fermé ou contact auxiliaire NC coupé.</t>
+          <t>🚨 Contacteur de puissance sens/vitesse M1 resté collé fermé ou boucle de surveillance EDM ouverte.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas enclencher la puissance. Couper les commandes en cabine.</t>
+          <t>🛑 Ne pas enclencher la puissance. Condamner le pupitre de commande.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>🧰 Consigner armoire. Contrôler les pôles de puissance du contacteur KM_M1 et les auxiliaires NO. Remplacer si soudé.</t>
+          <t>⚠️ DANGER 400V : Consigner l'armoire + VAT. Contrôler les pôles de puissance KM_M1 et la chaîne des contacts miroirs NC en série. Remplacer le contacteur si soudé.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_ContactorsReleased_DI (Local_Digital_IO · %IX0.0) | Cmd: M1_RelayAscent/Descent_DQ (%QX0.0, %QX0.1)</t>
+          <t>Local_Digital_IO · Borne %IX0.0 (M1_ContactorsReleased_DI) ➔ Mesure : 24Vcc / 0V entre borne et 0V carte ➔ Attendu repos : 24V (Contacts miroirs NC fermés en série)</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -23468,22 +25172,22 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>🚨 Contacteur de puissance sens/vitesse M2 resté collé fermé ou contact auxiliaire NC coupé.</t>
+          <t>🚨 Contacteur de puissance sens/vitesse M2 resté collé fermé ou boucle de surveillance EDM ouverte.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>🛑 Ne pas enclencher la puissance. Couper les commandes en cabine.</t>
+          <t>🛑 Ne pas enclencher la puissance. Condamner le pupitre de commande.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>🧰 Consigner armoire. Contrôler les pôles de puissance du contacteur KM_M2 et les auxiliaires NO. Remplacer si soudé.</t>
+          <t>⚠️ DANGER 400V : Consigner l'armoire + VAT. Contrôler les pôles de puissance KM_M2 et la chaîne des contacts miroirs NC en série. Remplacer le contacteur si soudé.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Retour: M2_ContactorsReleased_DI (Local_Digital_IO · %IX0.2) | Cmd: M2_RelayAscent/Descent_DQ (%QX0.2, %QX0.3)</t>
+          <t>Local_Digital_IO · Borne %IX0.2 (M2_ContactorsReleased_DI) ➔ Mesure : 24Vcc / 0V entre borne et 0V carte ➔ Attendu repos : 24V (Contacts miroirs NC fermés en série)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -23528,7 +25232,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>⏳ Laisser refroidir 15 min. Vérifier absence de blocage mécanique visuel sur le treuil.</t>
+          <t>⏳ Laisser refroidir 15 min. Vérifier visuellement l'absence d'obstacle mécanique sur le treuil M1.</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -23538,7 +25242,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_ThermalOk_DI (Local_Digital_IO · %IX0.1 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.1 (M1_ThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC disjoncteur fermé)</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -23578,12 +25282,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>🔥 Disjoncteur moteur M2 déclenché ou défaut de la moto-ventilation forcée.</t>
+          <t>🔥 Disjoncteur moteur M2 déclenché ou défaut moto-ventilation forcée.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>⏳ Laisser refroidir 15 min. Vérifier que la benne n'est pas coincée.</t>
+          <t>⏳ Laisser refroidir 15 min. Vérifier visuellement que la benne n'est pas bloquée.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -23593,7 +25297,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Retour: M2_ThermalOk_DI (Local_Digital_IO · %IX0.3 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.3 (M2_ThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC disjoncteur fermé)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -23638,17 +25342,17 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas lancer de mouvement treuils ou translation.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuils ou translation au pupitre.</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>🧰 Armoire : mesurer résistance ohmique des bobines freins M1/M2/M3 et ponts redresseurs. Réarmer disjoncteur freins.</t>
+          <t>🧰 Armoire : mesurer résistance ohmique des bobines freins M1/M2/M3 et ponts redresseurs. Réarmer disjoncteur freins Q_Freins.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Retour: M1_M2_M3_BrakeThermalOk_DI (VH_0800END · %IX225.3 · contact NC)</t>
+          <t>VH_0800END · Borne %IX225.3 (M1_M2_M3_BrakeThermalOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Contact NC fermé)</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -23693,17 +25397,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>👀 Vérifier le voltmètre général en cabine et la source d'alimentation (groupe ou réseau quai).</t>
+          <t>👀 Vérifier le voltmètre réseau au poste de conduite et la source d'alimentation (groupe ou réseau quai).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>🧰 Armoire tête : vérifier LEDs relais phases. Mesurer 400V entre phases. Permuter 2 phases amont si inversion.</t>
+          <t>🧰 Armoire tête : vérifier LEDs relais de surveillance phases. Mesurer 400Vac équilibré entre phases. Permuter 2 phases amont si inversion.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Retour: PhaseRotationOk_DI (VH_0800END · %IX225.4 · contact NC)</t>
+          <t>VH_0800END · Borne %IX225.4 (PhaseRotationOk_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu normal : 24V (Relais phases actif)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -23743,12 +25447,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>🪢 Câble benne mou (benne posée au sol ou au fond de l'eau) ou roulette palpeuse anti-mou bloquée.</t>
+          <t>🪢 Câble benne détendu (benne posée au sol ou au fond de l'eau) ou roulette palpeuse anti-mou bloquée.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Passer en manuel lent / dérogation : retendre doucement le câble M2 jusqu'à extinction du voyant mou.</t>
+          <t>🕹️ Passer en manuel lent / dérogation au pupitre : retendre doucement le câble M2 jusqu'à extinction du voyant mou.</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -23758,7 +25462,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Retour: M2_TensionedCable_DI (Local_Digital_IO · %IX0.4 · contact NC)</t>
+          <t>Local_Digital_IO · Borne %IX0.4 (M2_TensionedCable_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu câble tendu : 24V (Contact NC fermé)</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -23798,22 +25502,22 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>📐 Combinaison capteurs translation M3 impossible (ex: Trémie et Maintenance actives en même temps).</t>
+          <t>🪣 Benne détectée non fermée à la mise sous tension (état ouvert ou indéterminé).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>👀 Vérifier visuellement la position du portique sur les rails de roulement.</t>
+          <t>🕹️ Mettre sélecteur treuil sur Benne (M2). Actionner la commande de fermeture benne jusqu'au voyant benne fermée.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>🧰 Voie de roulement : tester les détecteurs inductifs de cames translation M3. Nettoyer les capteurs et vérifier la boîte chariot.</t>
+          <t>💻 Vérifier cohérence valeur codeur M2 vs M1 (OffsetCloseM ~ 15 m) sur l'écran diagnostic IHM.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Entrées cames: M3_PosTremie..M3_PosMaintenance (VH_0808ETP · %IX224.0 à %IX224.4)</t>
+          <t>Diagnostic IHM · Variable _BucketState.IsClosed ➔ Attendu : TRUE après fermeture complète (Delta M2-M1 conforme)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -23853,22 +25557,22 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>🚨 DANGER CRITIQUE : contacteur général puissance fermé alors que la boucle arrêt d'urgence est ouverte (pôles soudés).</t>
+          <t>🚨 Arrêt d'urgence percuté sur le pupitre de commande ou chaîne de sécurité ouverte.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>🛑 COUPURE GÉNÉRALE IMMÉDIATE. Frapper coup de poing AU cabine ou couper disjoncteur général. Évacuer la machine.</t>
+          <t>👀 Vérifier et déverrouiller tous les coups de poing AU (pupitre, passerelle, armoire). Appuyer sur Réarmement AU.</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>⚠️ DANGER DE MORT. Consigner l'alimentation à la source. Remplacer contacteur ligne puissance KM_Power et contrôler le bloc sécurité AU.</t>
+          <t>🧰 Contrôler tension 24V sur boucle de sécurité AU et retombée des canaux du bloc de sécurité.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Retours: PowerContactorEngaged_DI (%IX225.6) et EmergencyChainClosed_DI (%IX225.7) sur VH_0800END</t>
+          <t>VH_0800END · Borne %IX225.7 (EmergencyChainClosed_DI) ➔ Mesure : 24Vcc entre borne et 0V carte ➔ Attendu réarmé : 24V</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -23908,22 +25612,22 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>📡 Perte communication bus codeur M1 ou coupure de l'alimentation 24V capteur.</t>
+          <t>📡 Joystick non détecté sur le bus CANopen (coupure alimentation 24V pupitre ou câble CAN coupé).</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>🛑 Ne pas passer en mode Semi-Auto ou Automatique.</t>
+          <t>🛑 Couper et réenclencher l'interrupteur d'alimentation du pupitre de commande. Relever le code d'erreur affiché.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>🧰 Treuil M1 : contrôler voyants LED sur codeur absolu (Node 1). Vérifier connecteur M12, blindage câble et alim 24V.</t>
+          <t>🧰 Contrôler 24Vcc sur connecteur manipulateur sous pupitre. Vérifier continuité CAN_H / CAN_L et résistance de terminaison 120 Ω.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Bus codeur: COD1_CODEUR (Node 1) | Alim 24V codeur M1</t>
+          <t>Bus CANopen Pupitre ➔ Mesure : 24Vcc alim broches 1-2 | 60 Ω entre CAN_H et CAN_L ligne éteinte</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -23963,22 +25667,22 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>📡 Perte communication bus codeur M2 ou connecteur M12 desserré sur touret.</t>
+          <t>📡 Codeur absolu EtherCAT treuil M1 non opérationnel (câble M12 Ethernet débranché ou perte alimentation 24V).</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>🛑 Ne pas passer en mode Semi-Auto ou Automatique.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuil M1. Vérifier voyant bus sur l'écran IHM.</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>🧰 Treuil M2 : contrôler voyants LED sur codeur absolu (Node 2). Inspecter le câble souple de touret et la connectique M12.</t>
+          <t>🧰 Treuil M1 : contrôler LED d'état sur le codeur COD1 (L/A clignotante = trafic actif). Tester cordon M12 et présence 24Vcc.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Bus codeur: COD2_CODEUR (Node 2) | Alim 24V codeur M2</t>
+          <t>Codeur COD1 Treuil M1 ➔ Port M12 IN (EtherCAT) ➔ Attendu : LED L/A Verte clignotante, 24Vcc présent sur broches d'alimentation</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -24018,22 +25722,22 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>🎯 Treuil M1 non référencé depuis mise sous tension ou position mesurée en dehors de l'épure autorisée.</t>
+          <t>📡 Codeur absolu EtherCAT treuil M2 non opérationnel (câble M12 Ethernet débranché ou perte alimentation 24V).</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>🕹️ Sélectionner l'écran Homing en cabine et lancer la procédure de référencement guidée M1.</t>
+          <t>🛑 Ne pas tenter de manœuvre treuil M2. Vérifier voyant bus sur l'écran IHM.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le capteur came zéro de homing M1. Vérifier l'offset de référence et les seuils de butées logicielles dans CODESYS.</t>
+          <t>🧰 Treuil M2 : contrôler LED d'état sur le codeur COD2 (L/A clignotante = trafic actif). Tester cordon M12 et présence 24Vcc.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Détecteur zéro homing: M1M2_TopPositionFree_DI (Local_Digital_IO · %IX0.7) | Config: GVL_Config</t>
+          <t>Codeur COD2 Treuil M2 ➔ Port M12 IN (EtherCAT) ➔ Attendu : LED L/A Verte clignotante, 24Vcc présent sur broches d'alimentation</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -24073,22 +25777,22 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>🎯 Treuil M2 non calibré (homing requis) ou position de benne hors plage admissible.</t>
+          <t>⚡ Variateur translation AC600 hors ligne ou en défaut (coupure réseau EtherCAT, disjoncteur variateur déclenché).</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>🕹️ Sélectionner l'écran Homing en cabine et lancer la procédure de référencement guidée M2.</t>
+          <t>🛑 Ne pas tenter de déplacer le chariot au pupitre. Relever le code variateur sur l'IHM.</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>🧰 Contrôler le capteur de référence zéro benne M2. Vérifier les limites de course logicielles haute et basse dans CODESYS.</t>
+          <t>🧰 Armoire : vérifier affichage LED sur le variateur AC600. Contrôler disjoncteur drive Q_Drive et câble RJ45 EtherCAT.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Détecteur zéro homing: M1M2_TopPositionFree_DI (Local_Digital_IO · %IX0.7) | Config: GVL_Config</t>
+          <t>Variateur AC600 ➔ Afficheur de façade (Attendu : état 'rdy' ou fréquence 0.0) | Câble RJ45 EtherCAT Port IN</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -25128,7 +26832,7 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
@@ -25171,7 +26875,7 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25">
@@ -25214,7 +26918,7 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
@@ -25386,7 +27090,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30">
@@ -25429,7 +27133,7 @@
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31">
@@ -25472,7 +27176,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32">
@@ -25515,7 +27219,7 @@
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33">
@@ -25558,7 +27262,7 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34">
@@ -25601,7 +27305,7 @@
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>433</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35">
@@ -25644,7 +27348,7 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36">
@@ -25687,7 +27391,7 @@
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37">
@@ -25730,7 +27434,7 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38">
@@ -25773,7 +27477,7 @@
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="39">
@@ -25816,7 +27520,7 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>473</v>
+        <v>488</v>
       </c>
     </row>
     <row r="40">
@@ -25859,7 +27563,7 @@
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
